--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -465,10 +465,10 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -491,10 +491,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -517,10 +517,10 @@
         <v>1</v>
       </c>
       <c r="G4">
+        <v>51</v>
+      </c>
+      <c r="H4">
         <v>49</v>
-      </c>
-      <c r="H4">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -543,10 +543,10 @@
         <v>0.75</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -569,10 +569,10 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
